--- a/cet4/result/23_修仙女帝_重生都市系统/23_修仙女帝_重生都市系统_学习版.xlsx
+++ b/cet4/result/23_修仙女帝_重生都市系统/23_修仙女帝_重生都市系统_学习版.xlsx
@@ -397,773 +397,563 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D39"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>wooden</v>
       </c>
       <c r="B2" t="str">
-        <v>wooden</v>
+        <v>/ˈwʊdn/</v>
       </c>
       <c r="C2" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>木制的</v>
       </c>
-      <c r="D2" t="str">
-        <v>wooden(木制的)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>oak</v>
       </c>
       <c r="B3" t="str">
-        <v>oak</v>
+        <v>/oʊk/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>橡树</v>
       </c>
-      <c r="D3" t="str">
-        <v>oak(橡树)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>road</v>
       </c>
       <c r="B4" t="str">
-        <v>road</v>
+        <v>/roʊd/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>道路</v>
       </c>
-      <c r="D4" t="str">
-        <v>road(道路)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>muddy</v>
       </c>
       <c r="B5" t="str">
-        <v>muddy</v>
+        <v>/ˈmʌdi/</v>
       </c>
       <c r="C5" t="str">
+        <v>vt./vi./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>泥泞的</v>
       </c>
-      <c r="D5" t="str">
-        <v>muddy(泥泞的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>pond</v>
       </c>
       <c r="B6" t="str">
-        <v>pond</v>
+        <v>/pɑːnd/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D6" t="str">
         <v>池塘</v>
       </c>
-      <c r="D6" t="str">
-        <v>pond(池塘)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>us</v>
       </c>
       <c r="B7" t="str">
-        <v>us</v>
+        <v>/əs,ʌs/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D7" t="str">
         <v>我们</v>
       </c>
-      <c r="D7" t="str">
-        <v>us(我们)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>select</v>
       </c>
       <c r="B8" t="str">
-        <v>select</v>
+        <v>/sɪˈlekt/</v>
       </c>
       <c r="C8" t="str">
+        <v>vt./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>选择</v>
       </c>
-      <c r="D8" t="str">
-        <v>select(选择)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>concept</v>
       </c>
       <c r="B9" t="str">
-        <v>concept</v>
+        <v>/ˈkɑːnsept/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>概念</v>
       </c>
-      <c r="D9" t="str">
-        <v>concept(概念)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>vessel</v>
       </c>
       <c r="B10" t="str">
-        <v>vessel</v>
+        <v>/ˈvesl/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>容器</v>
       </c>
-      <c r="D10" t="str">
-        <v>vessel(容器)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>level</v>
       </c>
       <c r="B11" t="str">
-        <v>level</v>
+        <v>/ˈlevl/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>水平</v>
       </c>
-      <c r="D11" t="str">
-        <v>level(水平)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>central</v>
       </c>
       <c r="B12" t="str">
-        <v>central</v>
+        <v>/ˈsentrəl/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>中心的</v>
       </c>
-      <c r="D12" t="str">
-        <v>central(中心的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>student</v>
       </c>
       <c r="B13" t="str">
-        <v>student</v>
+        <v>/ˈstuːdnt/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>学生</v>
       </c>
-      <c r="D13" t="str">
-        <v>student(学生)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>finger</v>
       </c>
       <c r="B14" t="str">
-        <v>finger</v>
+        <v>/ˈfɪŋɡər/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D14" t="str">
         <v>手指</v>
       </c>
-      <c r="D14" t="str">
-        <v>finger(手指)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>synthetic</v>
       </c>
       <c r="B15" t="str">
-        <v>synthetic</v>
+        <v>/sɪnˈθetɪk/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>合成的</v>
       </c>
-      <c r="D15" t="str">
-        <v>synthetic(合成的)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>few</v>
       </c>
       <c r="B16" t="str">
-        <v>few</v>
+        <v>/fjuː/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./adj./pron.</v>
+      </c>
+      <c r="D16" t="str">
         <v>少数</v>
       </c>
-      <c r="D16" t="str">
-        <v>few(少数)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>oriental</v>
       </c>
       <c r="B17" t="str">
-        <v>oriental</v>
+        <v>/ˌɔːriˈentl/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>东方的</v>
       </c>
-      <c r="D17" t="str">
-        <v>oriental(东方的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>scan</v>
       </c>
       <c r="B18" t="str">
-        <v>scan</v>
+        <v>/skæn/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D18" t="str">
         <v>浏览</v>
       </c>
-      <c r="D18" t="str">
-        <v>scan(浏览)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>stability</v>
       </c>
       <c r="B19" t="str">
-        <v>stability</v>
+        <v>/stəˈbɪləti/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>稳定性</v>
       </c>
-      <c r="D19" t="str">
-        <v>stability(稳定性)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>sudden</v>
       </c>
       <c r="B20" t="str">
-        <v>sudden</v>
+        <v>/ˈsʌdn/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>突然的</v>
       </c>
-      <c r="D20" t="str">
-        <v>sudden(突然的)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>garbage</v>
       </c>
       <c r="B21" t="str">
-        <v>garbage</v>
+        <v>/ˈɡɑːrbɪdʒ/</v>
       </c>
       <c r="C21" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>垃圾</v>
       </c>
-      <c r="D21" t="str">
-        <v>garbage(垃圾)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>apparent</v>
       </c>
       <c r="B22" t="str">
-        <v>apparent</v>
+        <v>/əˈpærənt/</v>
       </c>
       <c r="C22" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>显然的</v>
       </c>
-      <c r="D22" t="str">
-        <v>apparent(显然的)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>dormitory</v>
       </c>
       <c r="B23" t="str">
-        <v>dormitory</v>
+        <v>/ˈdɔːrmətɔːri/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>宿舍</v>
       </c>
-      <c r="D23" t="str">
-        <v>dormitory(宿舍)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>sometime</v>
       </c>
       <c r="B24" t="str">
-        <v>sometime</v>
+        <v>/ˈsʌmtaɪm/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D24" t="str">
         <v>某时</v>
       </c>
-      <c r="D24" t="str">
-        <v>sometime(某时)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>conference</v>
       </c>
       <c r="B25" t="str">
-        <v>oak</v>
+        <v>/ˈkɑːnfərəns/</v>
       </c>
       <c r="C25" t="str">
-        <v>橡树</v>
+        <v>n./vi.</v>
       </c>
       <c r="D25" t="str">
-        <v>oak(橡树)📢</v>
+        <v>会议</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>engage</v>
       </c>
       <c r="B26" t="str">
-        <v>conference</v>
+        <v>/ɪnˈɡeɪdʒ/</v>
       </c>
       <c r="C26" t="str">
-        <v>会议</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D26" t="str">
-        <v>conference(会议)📢</v>
+        <v>参与</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>drift</v>
       </c>
       <c r="B27" t="str">
-        <v>engage</v>
+        <v>/drɪft/</v>
       </c>
       <c r="C27" t="str">
-        <v>参与</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D27" t="str">
-        <v>engage(参与)📢</v>
+        <v>漂流</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>suddenly</v>
       </c>
       <c r="B28" t="str">
-        <v>pond</v>
+        <v>/ˈsʌdənli/</v>
       </c>
       <c r="C28" t="str">
-        <v>池塘</v>
+        <v>v./adv.</v>
       </c>
       <c r="D28" t="str">
-        <v>pond(池塘)📢</v>
+        <v>突然</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>pierce</v>
       </c>
       <c r="B29" t="str">
-        <v>few</v>
+        <v>/pɪrs/</v>
       </c>
       <c r="C29" t="str">
-        <v>很少</v>
+        <v>n./v.</v>
       </c>
       <c r="D29" t="str">
-        <v>few(很少)📢</v>
+        <v>刺穿</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>thrill</v>
       </c>
       <c r="B30" t="str">
-        <v>drift</v>
+        <v>/θrɪl/</v>
       </c>
       <c r="C30" t="str">
-        <v>漂流</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D30" t="str">
-        <v>drift(漂流)📢</v>
+        <v>激动</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>ceremony</v>
       </c>
       <c r="B31" t="str">
-        <v>suddenly</v>
+        <v>/ˈserəmoʊni/</v>
       </c>
       <c r="C31" t="str">
-        <v>突然</v>
+        <v>n.</v>
       </c>
       <c r="D31" t="str">
-        <v>suddenly(突然)📢</v>
+        <v>典礼</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>audience</v>
       </c>
       <c r="B32" t="str">
-        <v>stability</v>
+        <v>/ˈɔːdiəns/</v>
       </c>
       <c r="C32" t="str">
-        <v>稳定</v>
+        <v>n.</v>
       </c>
       <c r="D32" t="str">
-        <v>stability(稳定)📢</v>
+        <v>观众</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>elastic</v>
       </c>
       <c r="B33" t="str">
-        <v>pierce</v>
+        <v>/ɪˈlæstɪk/</v>
       </c>
       <c r="C33" t="str">
-        <v>刺穿</v>
+        <v>n./adj.</v>
       </c>
       <c r="D33" t="str">
-        <v>pierce(刺穿)📢</v>
+        <v>灵活的</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>materialism</v>
       </c>
       <c r="B34" t="str">
-        <v>thrill</v>
+        <v>/məˈtɪriəlɪzəm/</v>
       </c>
       <c r="C34" t="str">
-        <v>激动</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>thrill(激动)📢</v>
+        <v>唯物主义</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>socialism</v>
       </c>
       <c r="B35" t="str">
-        <v>level</v>
+        <v>/ˈsoʊʃəlɪzəm/</v>
       </c>
       <c r="C35" t="str">
-        <v>水平</v>
+        <v>n.</v>
       </c>
       <c r="D35" t="str">
-        <v>level(水平)📢</v>
+        <v>社会主义</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>similarly</v>
       </c>
       <c r="B36" t="str">
-        <v>ceremony</v>
+        <v>/ˈsɪmələrli/</v>
       </c>
       <c r="C36" t="str">
-        <v>典礼</v>
+        <v>v./adv.</v>
       </c>
       <c r="D36" t="str">
-        <v>ceremony(典礼)📢</v>
+        <v>同样地</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>belief</v>
       </c>
       <c r="B37" t="str">
-        <v>audience</v>
+        <v>/bɪˈliːf/</v>
       </c>
       <c r="C37" t="str">
-        <v>观众</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>audience(观众)📢</v>
+        <v>信仰</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>religion</v>
       </c>
       <c r="B38" t="str">
-        <v>elastic</v>
+        <v>/rɪˈlɪdʒən/</v>
       </c>
       <c r="C38" t="str">
-        <v>灵活的</v>
+        <v>n.</v>
       </c>
       <c r="D38" t="str">
-        <v>elastic(灵活的)📢</v>
+        <v>宗教</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>dinner</v>
       </c>
       <c r="B39" t="str">
-        <v>materialism</v>
+        <v>/ˈdɪnər/</v>
       </c>
       <c r="C39" t="str">
-        <v>唯物主义</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>materialism(唯物主义)📢</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>socialism</v>
-      </c>
-      <c r="C40" t="str">
-        <v>社会主义</v>
-      </c>
-      <c r="D40" t="str">
-        <v>socialism(社会主义)📢</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>similarly</v>
-      </c>
-      <c r="C41" t="str">
-        <v>同样地</v>
-      </c>
-      <c r="D41" t="str">
-        <v>similarly(同样地)📢</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>belief</v>
-      </c>
-      <c r="C42" t="str">
-        <v>信仰</v>
-      </c>
-      <c r="D42" t="str">
-        <v>belief(信仰)📢</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>oriental</v>
-      </c>
-      <c r="C43" t="str">
-        <v>东方的</v>
-      </c>
-      <c r="D43" t="str">
-        <v>oriental(东方的)📢</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>conference</v>
-      </c>
-      <c r="C44" t="str">
-        <v>会议</v>
-      </c>
-      <c r="D44" t="str">
-        <v>conference(会议)📢</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>religion</v>
-      </c>
-      <c r="C45" t="str">
-        <v>宗教</v>
-      </c>
-      <c r="D45" t="str">
-        <v>religion(宗教)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>materialism</v>
-      </c>
-      <c r="C46" t="str">
-        <v>物质主义</v>
-      </c>
-      <c r="D46" t="str">
-        <v>materialism(物质主义)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>drift</v>
-      </c>
-      <c r="C47" t="str">
-        <v>漂流</v>
-      </c>
-      <c r="D47" t="str">
-        <v>drift(漂流)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>stability</v>
-      </c>
-      <c r="C48" t="str">
-        <v>稳定</v>
-      </c>
-      <c r="D48" t="str">
-        <v>stability(稳定)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>pierce</v>
-      </c>
-      <c r="C49" t="str">
-        <v>刺穿</v>
-      </c>
-      <c r="D49" t="str">
-        <v>pierce(刺穿)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>dinner</v>
-      </c>
-      <c r="C50" t="str">
         <v>晚宴</v>
-      </c>
-      <c r="D50" t="str">
-        <v>dinner(晚宴)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>wooden</v>
-      </c>
-      <c r="C51" t="str">
-        <v>木制</v>
-      </c>
-      <c r="D51" t="str">
-        <v>wooden(木制)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>muddy</v>
-      </c>
-      <c r="C52" t="str">
-        <v>泥泞</v>
-      </c>
-      <c r="D52" t="str">
-        <v>muddy(泥泞)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>belief</v>
-      </c>
-      <c r="C53" t="str">
-        <v>信仰</v>
-      </c>
-      <c r="D53" t="str">
-        <v>belief(信仰)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>belief</v>
-      </c>
-      <c r="C54" t="str">
-        <v>信仰</v>
-      </c>
-      <c r="D54" t="str">
-        <v>belief(信仰)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D39"/>
   </ignoredErrors>
 </worksheet>
 </file>